--- a/data/import/brady.xlsx
+++ b/data/import/brady.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U102"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>pub</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,11 +605,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-103.pdf</t>
         </is>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -684,11 +694,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-109.pdf</t>
         </is>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -768,11 +783,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-121.pdf</t>
         </is>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -852,11 +872,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-122.pdf</t>
         </is>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -936,11 +961,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-145.pdf</t>
         </is>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1012,11 +1042,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-236.pdf</t>
         </is>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1093,11 +1128,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-312.pdf</t>
         </is>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1177,11 +1217,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-321.pdf</t>
         </is>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1261,11 +1306,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-338.pdf</t>
         </is>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1342,11 +1392,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-342.pdf</t>
         </is>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1418,11 +1473,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-344.pdf</t>
         </is>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1494,11 +1554,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-345.pdf</t>
         </is>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1579,11 +1644,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-350.pdf</t>
         </is>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1663,11 +1733,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-351.pdf</t>
         </is>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1747,11 +1822,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-362.pdf</t>
         </is>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1826,11 +1906,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-388.pdf</t>
         </is>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1910,11 +1995,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-390.pdf</t>
         </is>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1994,11 +2084,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-402.pdf</t>
         </is>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2078,11 +2173,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-403.pdf</t>
         </is>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2159,11 +2259,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-408.pdf</t>
         </is>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2243,11 +2348,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-412.pdf</t>
         </is>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2327,11 +2437,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-413.pdf</t>
         </is>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2408,11 +2523,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-414.pdf</t>
         </is>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2492,11 +2612,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-417.pdf</t>
         </is>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2576,11 +2701,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-421.pdf</t>
         </is>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2660,11 +2790,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-422.pdf</t>
         </is>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2744,11 +2879,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-423.pdf</t>
         </is>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2828,11 +2968,16 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-424.pdf</t>
         </is>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2912,11 +3057,16 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-425A.pdf</t>
         </is>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2996,11 +3146,16 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-427.pdf</t>
         </is>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3080,11 +3235,16 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-428.pdf</t>
         </is>
-      </c>
-      <c r="U32" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3164,11 +3324,16 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-430.pdf</t>
         </is>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3248,11 +3413,16 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-432.pdf</t>
         </is>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3332,11 +3502,16 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-434A.pdf</t>
         </is>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3416,11 +3591,16 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-435A.pdf</t>
         </is>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3495,11 +3675,16 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-437.pdf</t>
         </is>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3579,11 +3764,16 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-438.pdf</t>
         </is>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3663,11 +3853,16 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-439.pdf</t>
         </is>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3747,11 +3942,16 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-449.pdf</t>
         </is>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3831,11 +4031,16 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-461.pdf</t>
         </is>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3915,11 +4120,16 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-472.pdf</t>
         </is>
-      </c>
-      <c r="U42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3999,11 +4209,16 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-473.pdf</t>
         </is>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4083,11 +4298,16 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-480A.pdf</t>
         </is>
-      </c>
-      <c r="U44" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4167,11 +4387,16 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-481.pdf</t>
         </is>
-      </c>
-      <c r="U45" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4245,12 +4470,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>https://tds.bradyid.com/TDSdocs/B-482.pdf</t>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://tds.bradyid.com/TDSdocs/B-482.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4329,11 +4559,16 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-483A.pdf</t>
         </is>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4413,11 +4648,16 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-484A.pdf</t>
         </is>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4497,11 +4737,16 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-486B.pdf</t>
         </is>
-      </c>
-      <c r="U49" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4581,11 +4826,16 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-488.pdf</t>
         </is>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4665,11 +4915,16 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-489A.pdf</t>
         </is>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4749,11 +5004,16 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-490.pdf</t>
         </is>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4828,11 +5088,16 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-492.pdf</t>
         </is>
-      </c>
-      <c r="U53" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4912,11 +5177,16 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-498.pdf</t>
         </is>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4991,12 +5261,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://tds.bradyid.com/TDSdocs/B-499.pdf</t>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>0</v>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>https://tds.bradyid.com/TDSdocs/B-499.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5070,11 +5345,16 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-500.pdf</t>
         </is>
-      </c>
-      <c r="U56" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -5149,12 +5429,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://tds.bradyid.com/TDSdocs/B-508.pdf</t>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>0</v>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://tds.bradyid.com/TDSdocs/B-508.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5233,11 +5518,16 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-530.pdf</t>
         </is>
-      </c>
-      <c r="U58" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -5317,11 +5607,16 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-533.pdf</t>
         </is>
-      </c>
-      <c r="U59" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5401,11 +5696,16 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-593.pdf</t>
         </is>
-      </c>
-      <c r="U60" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5485,11 +5785,16 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-619A.pdf</t>
         </is>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -5569,11 +5874,16 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-637.pdf</t>
         </is>
-      </c>
-      <c r="U62" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5653,11 +5963,16 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-642.pdf</t>
         </is>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -5737,11 +6052,16 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-652.pdf</t>
         </is>
-      </c>
-      <c r="U64" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5813,11 +6133,16 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-654.pdf</t>
         </is>
-      </c>
-      <c r="U65" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -5897,11 +6222,16 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-719.pdf</t>
         </is>
-      </c>
-      <c r="U66" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -5981,11 +6311,16 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-724.pdf</t>
         </is>
-      </c>
-      <c r="U67" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -6065,11 +6400,16 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-728.pdf</t>
         </is>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -6149,11 +6489,16 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-729.pdf</t>
         </is>
-      </c>
-      <c r="U69" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -6233,11 +6578,16 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-730.pdf</t>
         </is>
-      </c>
-      <c r="U70" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6317,11 +6667,16 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-731.pdf</t>
         </is>
-      </c>
-      <c r="U71" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6391,12 +6746,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>https://tds.bradyid.com/TDSdocs/B-7316.pdf</t>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
         </is>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://tds.bradyid.com/TDSdocs/B-7316.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6475,11 +6835,16 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-732A.pdf</t>
         </is>
-      </c>
-      <c r="U73" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -6559,11 +6924,16 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-733A.pdf</t>
         </is>
-      </c>
-      <c r="U74" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -6643,11 +7013,16 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-734.pdf</t>
         </is>
-      </c>
-      <c r="U75" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6727,11 +7102,16 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-735.pdf</t>
         </is>
-      </c>
-      <c r="U76" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -6811,11 +7191,16 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7425.pdf</t>
         </is>
-      </c>
-      <c r="U77" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -6895,11 +7280,16 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7511.pdf</t>
         </is>
-      </c>
-      <c r="U78" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6979,11 +7369,16 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7512.pdf</t>
         </is>
-      </c>
-      <c r="U79" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -7063,11 +7458,16 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7518.pdf</t>
         </is>
-      </c>
-      <c r="U80" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -7147,11 +7547,16 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7546.pdf</t>
         </is>
-      </c>
-      <c r="U81" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -7233,11 +7638,16 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7566.pdf</t>
         </is>
-      </c>
-      <c r="U82" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -7317,11 +7727,16 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7576.pdf</t>
         </is>
-      </c>
-      <c r="U83" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -7398,11 +7813,16 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7641.pdf</t>
         </is>
-      </c>
-      <c r="U84" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -7474,11 +7894,16 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7642.pdf</t>
         </is>
-      </c>
-      <c r="U85" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -7553,11 +7978,16 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7643.pdf</t>
         </is>
-      </c>
-      <c r="U86" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -7637,11 +8067,16 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7646.pdf</t>
         </is>
-      </c>
-      <c r="U87" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -7721,11 +8156,16 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-767.pdf</t>
         </is>
-      </c>
-      <c r="U88" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -7805,11 +8245,16 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-768.pdf</t>
         </is>
-      </c>
-      <c r="U89" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -7889,11 +8334,16 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-776.pdf</t>
         </is>
-      </c>
-      <c r="U90" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -7973,11 +8423,16 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-777.pdf</t>
         </is>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -8057,11 +8512,16 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-797.pdf</t>
         </is>
-      </c>
-      <c r="U92" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -8141,11 +8601,16 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-8117.pdf</t>
         </is>
-      </c>
-      <c r="U93" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -8225,11 +8690,16 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-813.pdf</t>
         </is>
-      </c>
-      <c r="U94" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -8309,11 +8779,16 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-816.pdf</t>
         </is>
-      </c>
-      <c r="U95" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8393,11 +8868,16 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-8423.pdf</t>
         </is>
-      </c>
-      <c r="U96" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -8477,11 +8957,16 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-8425.pdf</t>
         </is>
-      </c>
-      <c r="U97" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -8561,11 +9046,16 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-8459.pdf</t>
         </is>
-      </c>
-      <c r="U98" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -8645,11 +9135,16 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-8591.pdf</t>
         </is>
-      </c>
-      <c r="U99" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -8724,11 +9219,16 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-953.pdf</t>
         </is>
-      </c>
-      <c r="U100" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -8808,11 +9308,16 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-966B.pdf</t>
         </is>
-      </c>
-      <c r="U101" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -8892,11 +9397,16 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
+          <t>https://d37iyw84027v1q.cloudfront.net/Common/msapp/index.html</t>
+        </is>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
           <t>https://tds.bradyid.com/TDSdocs/B-969A.pdf</t>
         </is>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/import/brady.xlsx
+++ b/data/import/brady.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:W102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>tds</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -616,6 +621,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-103.pdf</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-109.pdf</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -794,6 +809,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-121.pdf</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -883,6 +903,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-122.pdf</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -972,6 +997,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-145.pdf</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1053,6 +1083,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-236.pdf</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1139,6 +1174,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-312.pdf</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1228,6 +1268,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-321.pdf</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1317,6 +1362,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-338.pdf</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1403,6 +1453,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-342.pdf</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1484,6 +1539,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-344.pdf</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1565,6 +1625,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-345.pdf</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1655,6 +1720,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-350.pdf</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1744,6 +1814,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-351.pdf</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Inspection Repair</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1833,6 +1908,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-362.pdf</t>
         </is>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1917,6 +1997,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-388.pdf</t>
         </is>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2006,6 +2091,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-390.pdf</t>
         </is>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2095,6 +2185,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-402.pdf</t>
         </is>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2184,6 +2279,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-403.pdf</t>
         </is>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2270,6 +2370,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-408.pdf</t>
         </is>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2359,6 +2464,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-412.pdf</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2448,6 +2558,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-413.pdf</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2534,6 +2649,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-414.pdf</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2623,6 +2743,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-417.pdf</t>
         </is>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2712,6 +2837,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-421.pdf</t>
         </is>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2801,6 +2931,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-422.pdf</t>
         </is>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2890,6 +3025,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-423.pdf</t>
         </is>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2979,6 +3119,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-424.pdf</t>
         </is>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3068,6 +3213,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-425A.pdf</t>
         </is>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3157,6 +3307,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-427.pdf</t>
         </is>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3246,6 +3401,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-428.pdf</t>
         </is>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3335,6 +3495,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-430.pdf</t>
         </is>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3424,6 +3589,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-432.pdf</t>
         </is>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3513,6 +3683,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-434A.pdf</t>
         </is>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3602,6 +3777,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-435A.pdf</t>
         </is>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3686,6 +3866,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-437.pdf</t>
         </is>
       </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3775,6 +3960,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-438.pdf</t>
         </is>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3864,6 +4054,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-439.pdf</t>
         </is>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3953,6 +4148,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-449.pdf</t>
         </is>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4042,6 +4242,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-461.pdf</t>
         </is>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4131,6 +4336,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-472.pdf</t>
         </is>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4220,6 +4430,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-473.pdf</t>
         </is>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4309,6 +4524,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-480A.pdf</t>
         </is>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4398,6 +4618,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-481.pdf</t>
         </is>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4481,6 +4706,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-482.pdf</t>
         </is>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4570,6 +4800,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-483A.pdf</t>
         </is>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4659,6 +4894,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-484A.pdf</t>
         </is>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4748,6 +4988,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-486B.pdf</t>
         </is>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4837,6 +5082,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-488.pdf</t>
         </is>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4926,6 +5176,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-489A.pdf</t>
         </is>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5015,6 +5270,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-490.pdf</t>
         </is>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5099,6 +5359,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-492.pdf</t>
         </is>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5188,6 +5453,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-498.pdf</t>
         </is>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5272,6 +5542,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-499.pdf</t>
         </is>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5356,6 +5631,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-500.pdf</t>
         </is>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5440,6 +5720,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-508.pdf</t>
         </is>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5529,6 +5814,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-530.pdf</t>
         </is>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5618,6 +5908,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-533.pdf</t>
         </is>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5707,6 +6002,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-593.pdf</t>
         </is>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5796,6 +6096,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-619A.pdf</t>
         </is>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5885,6 +6190,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-637.pdf</t>
         </is>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5974,6 +6284,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-642.pdf</t>
         </is>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6063,6 +6378,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-652.pdf</t>
         </is>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6144,6 +6464,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-654.pdf</t>
         </is>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6233,6 +6558,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-719.pdf</t>
         </is>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6322,6 +6652,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-724.pdf</t>
         </is>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6411,6 +6746,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-728.pdf</t>
         </is>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6500,6 +6840,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-729.pdf</t>
         </is>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6589,6 +6934,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-730.pdf</t>
         </is>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6678,6 +7028,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-731.pdf</t>
         </is>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6846,6 +7201,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-732A.pdf</t>
         </is>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6935,6 +7295,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-733A.pdf</t>
         </is>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7024,6 +7389,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-734.pdf</t>
         </is>
       </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7113,6 +7483,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-735.pdf</t>
         </is>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7202,6 +7577,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7425.pdf</t>
         </is>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7291,6 +7671,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7511.pdf</t>
         </is>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Inspection Repair</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7380,6 +7765,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7512.pdf</t>
         </is>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Inspection Repair</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7469,6 +7859,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7518.pdf</t>
         </is>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Inspection Repair</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7556,6 +7951,11 @@
       <c r="V81" t="inlineStr">
         <is>
           <t>https://tds.bradyid.com/TDSdocs/B-7546.pdf</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>General Identification</t>
         </is>
       </c>
     </row>
@@ -7649,6 +8049,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7566.pdf</t>
         </is>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7738,6 +8143,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7576.pdf</t>
         </is>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7824,6 +8234,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7641.pdf</t>
         </is>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7905,6 +8320,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7642.pdf</t>
         </is>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7989,6 +8409,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7643.pdf</t>
         </is>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8078,6 +8503,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-7646.pdf</t>
         </is>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Wire &amp; Cable</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8167,6 +8597,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-767.pdf</t>
         </is>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8256,6 +8691,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-768.pdf</t>
         </is>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8345,6 +8785,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-776.pdf</t>
         </is>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8434,6 +8879,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-777.pdf</t>
         </is>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8523,6 +8973,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-797.pdf</t>
         </is>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Circuit Board</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8612,6 +9067,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-8117.pdf</t>
         </is>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8701,6 +9161,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-813.pdf</t>
         </is>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8790,6 +9255,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-816.pdf</t>
         </is>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8879,6 +9349,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-8423.pdf</t>
         </is>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8968,6 +9443,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-8425.pdf</t>
         </is>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9057,6 +9537,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-8459.pdf</t>
         </is>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9146,6 +9631,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-8591.pdf</t>
         </is>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9230,6 +9720,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-953.pdf</t>
         </is>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Inspection Repair</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9319,6 +9814,11 @@
           <t>https://tds.bradyid.com/TDSdocs/B-966B.pdf</t>
         </is>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>General Identification</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9406,6 +9906,11 @@
       <c r="V102" t="inlineStr">
         <is>
           <t>https://tds.bradyid.com/TDSdocs/B-969A.pdf</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>General Identification</t>
         </is>
       </c>
     </row>

--- a/data/import/brady.xlsx
+++ b/data/import/brady.xlsx
@@ -1499,7 +1499,7 @@
         <v>-55</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
